--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373235</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373239</v>
       </c>
       <c r="B4" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373232</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137373234</v>
       </c>
       <c r="B6" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137373236</v>
       </c>
       <c r="B7" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137373238</v>
       </c>
       <c r="B8" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137373292</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137373231</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137373241</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>137373291</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373235</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373239</v>
       </c>
       <c r="B4" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373232</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137373234</v>
       </c>
       <c r="B6" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137373236</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137373238</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137373292</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373235</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373239</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373232</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137373234</v>
       </c>
       <c r="B6" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137373236</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137373238</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137373292</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373235</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373239</v>
       </c>
       <c r="B4" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373232</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137373234</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137373236</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137373238</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137373292</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35738-2026 artfynd.xlsx
+++ b/artfynd/A 35738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373293</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373235</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373239</v>
       </c>
       <c r="B4" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373232</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137373234</v>
       </c>
       <c r="B6" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137373236</v>
       </c>
       <c r="B7" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137373238</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>137373292</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137373231</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137373241</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>137373291</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
